--- a/artfynd/A 54825-2024 artfynd.xlsx
+++ b/artfynd/A 54825-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121790366</v>
+        <v>121795515</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661345</v>
+        <v>661263</v>
       </c>
       <c r="R2" t="n">
-        <v>6685822</v>
+        <v>6685776</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,9 +760,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +787,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121789972</v>
+        <v>121795513</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>5193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,50 +811,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661253</v>
+        <v>661240</v>
       </c>
       <c r="R3" t="n">
-        <v>6685725</v>
+        <v>6685794</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,9 +881,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,19 +908,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121795555</v>
+        <v>121790076</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -932,30 +955,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661316</v>
+        <v>661273</v>
       </c>
       <c r="R4" t="n">
-        <v>6685756</v>
+        <v>6685772</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,19 +1002,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121795515</v>
+        <v>121790393</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>100379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,53 +1043,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661263</v>
+        <v>661367</v>
       </c>
       <c r="R5" t="n">
-        <v>6685776</v>
+        <v>6685793</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,19 +1104,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121795517</v>
+        <v>121795555</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,39 +1145,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1197,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661348</v>
+        <v>661316</v>
       </c>
       <c r="R6" t="n">
-        <v>6685767</v>
+        <v>6685756</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1232,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121795513</v>
+        <v>121795517</v>
       </c>
       <c r="B7" t="n">
-        <v>5193</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,20 +1269,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1302,13 +1290,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1318,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661240</v>
+        <v>661348</v>
       </c>
       <c r="R7" t="n">
-        <v>6685794</v>
+        <v>6685767</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1353,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121790393</v>
+        <v>121789972</v>
       </c>
       <c r="B8" t="n">
-        <v>100379</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,38 +1393,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661367</v>
+        <v>661253</v>
       </c>
       <c r="R8" t="n">
-        <v>6685793</v>
+        <v>6685725</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1492,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121790076</v>
+        <v>121790366</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661273</v>
+        <v>661345</v>
       </c>
       <c r="R9" t="n">
-        <v>6685772</v>
+        <v>6685822</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 54825-2024 artfynd.xlsx
+++ b/artfynd/A 54825-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121795515</v>
+        <v>121795517</v>
       </c>
       <c r="B2" t="n">
         <v>57373</v>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661263</v>
+        <v>661348</v>
       </c>
       <c r="R2" t="n">
-        <v>6685776</v>
+        <v>6685767</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -920,7 +920,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121790076</v>
+        <v>121789972</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -955,7 +955,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661273</v>
+        <v>661253</v>
       </c>
       <c r="R4" t="n">
-        <v>6685772</v>
+        <v>6685725</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121790393</v>
+        <v>121790076</v>
       </c>
       <c r="B5" t="n">
-        <v>100379</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,38 +1043,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661367</v>
+        <v>661273</v>
       </c>
       <c r="R5" t="n">
-        <v>6685793</v>
+        <v>6685772</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121795555</v>
+        <v>121790393</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>100379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,53 +1154,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661316</v>
+        <v>661367</v>
       </c>
       <c r="R6" t="n">
-        <v>6685756</v>
+        <v>6685793</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,19 +1215,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,22 +1232,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121795517</v>
+        <v>121790366</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,53 +1256,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661348</v>
+        <v>661345</v>
       </c>
       <c r="R7" t="n">
-        <v>6685767</v>
+        <v>6685822</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,19 +1326,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,19 +1343,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121789972</v>
+        <v>121795555</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1416,27 +1390,30 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661253</v>
+        <v>661316</v>
       </c>
       <c r="R8" t="n">
-        <v>6685725</v>
+        <v>6685756</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,9 +1440,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121790366</v>
+        <v>121795515</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,50 +1491,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661345</v>
+        <v>661263</v>
       </c>
       <c r="R9" t="n">
-        <v>6685822</v>
+        <v>6685776</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,9 +1564,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,12 +1591,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 54825-2024 artfynd.xlsx
+++ b/artfynd/A 54825-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121795517</v>
+        <v>121795513</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,16 +708,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661348</v>
+        <v>661240</v>
       </c>
       <c r="R2" t="n">
-        <v>6685767</v>
+        <v>6685794</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121795513</v>
+        <v>121790393</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
+        <v>100379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,46 +812,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661240</v>
+        <v>661367</v>
       </c>
       <c r="R3" t="n">
-        <v>6685794</v>
+        <v>6685793</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,19 +869,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,19 +886,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121789972</v>
+        <v>121795555</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -955,27 +933,30 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661253</v>
+        <v>661316</v>
       </c>
       <c r="R4" t="n">
-        <v>6685725</v>
+        <v>6685756</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,9 +983,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,22 +1010,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121790076</v>
+        <v>121795515</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,50 +1034,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661273</v>
+        <v>661263</v>
       </c>
       <c r="R5" t="n">
-        <v>6685772</v>
+        <v>6685776</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,9 +1107,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,22 +1134,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121790393</v>
+        <v>121795517</v>
       </c>
       <c r="B6" t="n">
-        <v>100379</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,41 +1158,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661367</v>
+        <v>661348</v>
       </c>
       <c r="R6" t="n">
-        <v>6685793</v>
+        <v>6685767</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,9 +1231,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,12 +1258,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1355,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121795555</v>
+        <v>121789972</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1390,30 +1416,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661316</v>
+        <v>661253</v>
       </c>
       <c r="R8" t="n">
-        <v>6685756</v>
+        <v>6685725</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,19 +1463,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,22 +1480,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121795515</v>
+        <v>121790064</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,53 +1504,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661263</v>
+        <v>661273</v>
       </c>
       <c r="R9" t="n">
-        <v>6685776</v>
+        <v>6685772</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,19 +1574,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,12 +1591,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 54825-2024 artfynd.xlsx
+++ b/artfynd/A 54825-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121795513</v>
+        <v>121795517</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,13 +708,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -724,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661240</v>
+        <v>661348</v>
       </c>
       <c r="R2" t="n">
-        <v>6685794</v>
+        <v>6685767</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121790393</v>
+        <v>121795555</v>
       </c>
       <c r="B3" t="n">
-        <v>100379</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,41 +811,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661367</v>
+        <v>661316</v>
       </c>
       <c r="R3" t="n">
-        <v>6685793</v>
+        <v>6685756</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,9 +884,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,19 +911,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121795555</v>
+        <v>121790064</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -933,30 +958,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661316</v>
+        <v>661273</v>
       </c>
       <c r="R4" t="n">
-        <v>6685756</v>
+        <v>6685772</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,19 +1005,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,22 +1022,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121795515</v>
+        <v>121790366</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,53 +1046,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661263</v>
+        <v>661345</v>
       </c>
       <c r="R5" t="n">
-        <v>6685776</v>
+        <v>6685822</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,19 +1116,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,22 +1133,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121795517</v>
+        <v>121790393</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>100379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,53 +1157,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661348</v>
+        <v>661367</v>
       </c>
       <c r="R6" t="n">
-        <v>6685767</v>
+        <v>6685793</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,19 +1218,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,22 +1235,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121790366</v>
+        <v>121795515</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,50 +1259,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661345</v>
+        <v>661263</v>
       </c>
       <c r="R7" t="n">
-        <v>6685822</v>
+        <v>6685776</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,9 +1332,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,22 +1359,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121789972</v>
+        <v>121795513</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>5193</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,50 +1383,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661253</v>
+        <v>661240</v>
       </c>
       <c r="R8" t="n">
-        <v>6685725</v>
+        <v>6685794</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,9 +1453,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,19 +1480,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121790064</v>
+        <v>121789972</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661273</v>
+        <v>661253</v>
       </c>
       <c r="R9" t="n">
-        <v>6685772</v>
+        <v>6685725</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 54825-2024 artfynd.xlsx
+++ b/artfynd/A 54825-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121795555</v>
+        <v>121790366</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -834,30 +834,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661316</v>
+        <v>661345</v>
       </c>
       <c r="R3" t="n">
-        <v>6685756</v>
+        <v>6685822</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,19 +881,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,22 +898,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121790064</v>
+        <v>121790393</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>100379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,47 +922,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661273</v>
+        <v>661367</v>
       </c>
       <c r="R4" t="n">
-        <v>6685772</v>
+        <v>6685793</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1034,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121790366</v>
+        <v>121795515</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,50 +1024,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661345</v>
+        <v>661263</v>
       </c>
       <c r="R5" t="n">
-        <v>6685822</v>
+        <v>6685776</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,9 +1097,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,22 +1124,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121790393</v>
+        <v>121790076</v>
       </c>
       <c r="B6" t="n">
-        <v>100379</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,38 +1148,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661367</v>
+        <v>661273</v>
       </c>
       <c r="R6" t="n">
-        <v>6685793</v>
+        <v>6685772</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121795515</v>
+        <v>121789972</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,53 +1259,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661263</v>
+        <v>661253</v>
       </c>
       <c r="R7" t="n">
-        <v>6685776</v>
+        <v>6685725</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,19 +1329,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,12 +1346,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1492,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121789972</v>
+        <v>121795555</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1527,27 +1514,30 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661253</v>
+        <v>661316</v>
       </c>
       <c r="R9" t="n">
-        <v>6685725</v>
+        <v>6685756</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,9 +1564,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,12 +1591,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 54825-2024 artfynd.xlsx
+++ b/artfynd/A 54825-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121795517</v>
+        <v>121795515</v>
       </c>
       <c r="B2" t="n">
         <v>57373</v>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661348</v>
+        <v>661263</v>
       </c>
       <c r="R2" t="n">
-        <v>6685767</v>
+        <v>6685776</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121790366</v>
+        <v>121795517</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,50 +811,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661345</v>
+        <v>661348</v>
       </c>
       <c r="R3" t="n">
-        <v>6685822</v>
+        <v>6685767</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,9 +884,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,12 +911,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1012,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121795515</v>
+        <v>121795555</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,39 +1037,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1064,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661263</v>
+        <v>661316</v>
       </c>
       <c r="R5" t="n">
-        <v>6685776</v>
+        <v>6685756</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1099,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1149,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121790076</v>
+        <v>121790366</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1171,7 +1184,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1185,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661273</v>
+        <v>661345</v>
       </c>
       <c r="R6" t="n">
-        <v>6685772</v>
+        <v>6685822</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121789972</v>
+        <v>121795513</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>5193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,50 +1272,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661253</v>
+        <v>661240</v>
       </c>
       <c r="R7" t="n">
-        <v>6685725</v>
+        <v>6685794</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,9 +1342,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,22 +1369,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121795513</v>
+        <v>121790076</v>
       </c>
       <c r="B8" t="n">
-        <v>5193</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,50 +1393,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661240</v>
+        <v>661273</v>
       </c>
       <c r="R8" t="n">
-        <v>6685794</v>
+        <v>6685772</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,19 +1463,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,19 +1480,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121795555</v>
+        <v>121789972</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1514,30 +1527,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661316</v>
+        <v>661253</v>
       </c>
       <c r="R9" t="n">
-        <v>6685756</v>
+        <v>6685725</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,19 +1574,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,12 +1591,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 54825-2024 artfynd.xlsx
+++ b/artfynd/A 54825-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121795515</v>
+        <v>121795513</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,16 +708,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661263</v>
+        <v>661240</v>
       </c>
       <c r="R2" t="n">
-        <v>6685776</v>
+        <v>6685794</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121795517</v>
+        <v>121795515</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -851,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661348</v>
+        <v>661263</v>
       </c>
       <c r="R3" t="n">
-        <v>6685767</v>
+        <v>6685776</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -886,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121790393</v>
+        <v>121790076</v>
       </c>
       <c r="B4" t="n">
-        <v>100379</v>
+        <v>98131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,38 +932,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661367</v>
+        <v>661273</v>
       </c>
       <c r="R4" t="n">
-        <v>6685793</v>
+        <v>6685772</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,7 +1034,7 @@
         <v>121795555</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1149,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121790366</v>
+        <v>121795517</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>57381</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,50 +1167,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661345</v>
+        <v>661348</v>
       </c>
       <c r="R6" t="n">
-        <v>6685822</v>
+        <v>6685767</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,9 +1240,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,22 +1267,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121795513</v>
+        <v>121789972</v>
       </c>
       <c r="B7" t="n">
-        <v>5193</v>
+        <v>98131</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,50 +1291,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661240</v>
+        <v>661253</v>
       </c>
       <c r="R7" t="n">
-        <v>6685794</v>
+        <v>6685725</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,19 +1361,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,22 +1378,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121790076</v>
+        <v>121790393</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>100397</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,47 +1402,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661273</v>
+        <v>661367</v>
       </c>
       <c r="R8" t="n">
-        <v>6685772</v>
+        <v>6685793</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,10 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121789972</v>
+        <v>121790366</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661253</v>
+        <v>661345</v>
       </c>
       <c r="R9" t="n">
-        <v>6685725</v>
+        <v>6685822</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 54825-2024 artfynd.xlsx
+++ b/artfynd/A 54825-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121795513</v>
+        <v>121790064</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>98133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661240</v>
+        <v>661273</v>
       </c>
       <c r="R2" t="n">
-        <v>6685794</v>
+        <v>6685772</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,19 +757,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,19 +774,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121795515</v>
+        <v>121795517</v>
       </c>
       <c r="B3" t="n">
         <v>57381</v>
@@ -848,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661263</v>
+        <v>661348</v>
       </c>
       <c r="R3" t="n">
-        <v>6685776</v>
+        <v>6685767</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -883,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121790076</v>
+        <v>121789972</v>
       </c>
       <c r="B4" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,7 +945,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -969,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661273</v>
+        <v>661253</v>
       </c>
       <c r="R4" t="n">
-        <v>6685772</v>
+        <v>6685725</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121795555</v>
+        <v>121795515</v>
       </c>
       <c r="B5" t="n">
-        <v>98131</v>
+        <v>57381</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,39 +1033,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1083,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661316</v>
+        <v>661263</v>
       </c>
       <c r="R5" t="n">
-        <v>6685756</v>
+        <v>6685776</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1118,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121795517</v>
+        <v>121790366</v>
       </c>
       <c r="B6" t="n">
-        <v>57381</v>
+        <v>98133</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,53 +1157,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661348</v>
+        <v>661345</v>
       </c>
       <c r="R6" t="n">
-        <v>6685767</v>
+        <v>6685822</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,19 +1227,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,22 +1244,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121789972</v>
+        <v>121795555</v>
       </c>
       <c r="B7" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1314,27 +1291,30 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661253</v>
+        <v>661316</v>
       </c>
       <c r="R7" t="n">
-        <v>6685725</v>
+        <v>6685756</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,9 +1341,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,22 +1368,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121790393</v>
+        <v>121795513</v>
       </c>
       <c r="B8" t="n">
-        <v>100397</v>
+        <v>5193</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,37 +1396,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661367</v>
+        <v>661240</v>
       </c>
       <c r="R8" t="n">
-        <v>6685793</v>
+        <v>6685794</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,9 +1462,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,22 +1489,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121790366</v>
+        <v>121790393</v>
       </c>
       <c r="B9" t="n">
-        <v>98131</v>
+        <v>100399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,47 +1513,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661345</v>
+        <v>661367</v>
       </c>
       <c r="R9" t="n">
-        <v>6685822</v>
+        <v>6685793</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
